--- a/exports/trend_1d/HDFCLIFE_full_report.xlsx
+++ b/exports/trend_1d/HDFCLIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.52</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H2" t="n">
-        <v>445.35</v>
+        <v>421.85</v>
       </c>
       <c r="I2" t="n">
         <v>433.325500085529</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>19.48</v>
+        <v>13.17</v>
       </c>
       <c r="L2" t="n">
         <v>4.19</v>
@@ -555,7 +578,7 @@
         <v>1.22</v>
       </c>
       <c r="N2" t="n">
-        <v>2.67</v>
+        <v>5.28</v>
       </c>
       <c r="O2" t="n">
         <v>0.34</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>14.8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H3" t="n">
-        <v>454.45</v>
+        <v>482.65</v>
       </c>
       <c r="I3" t="n">
         <v>462.20129104762</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.73</v>
+        <v>-14.41</v>
       </c>
       <c r="L3" t="n">
-        <v>13.26</v>
+        <v>15.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>4.98</v>
+        <v>6.21</v>
       </c>
       <c r="O3" t="n">
         <v>-5.28</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H4" t="n">
-        <v>493.95</v>
+        <v>489.65</v>
       </c>
       <c r="I4" t="n">
         <v>492.4391738538621</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>2.34</v>
+        <v>1.45</v>
       </c>
       <c r="L4" t="n">
         <v>5.4</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.85</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43305</v>
+        <v>43306</v>
       </c>
       <c r="H5" t="n">
-        <v>480.15</v>
+        <v>494.35</v>
       </c>
       <c r="I5" t="n">
         <v>494.1360081810513</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>1.94</v>
+        <v>-0.96</v>
       </c>
       <c r="L5" t="n">
         <v>3.91</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.25</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H6" t="n">
-        <v>460.15</v>
+        <v>452.9</v>
       </c>
       <c r="I6" t="n">
         <v>456.124266906873</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.92</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>7.15</v>
+        <v>8.57</v>
       </c>
       <c r="M6" t="n">
         <v>0.48</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H7" t="n">
-        <v>386.6</v>
+        <v>399.15</v>
       </c>
       <c r="I7" t="n">
         <v>395.44949479168</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K7" t="n">
-        <v>14.64</v>
+        <v>11.87</v>
       </c>
       <c r="L7" t="n">
         <v>2.02</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.67</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43482</v>
+        <v>43483</v>
       </c>
       <c r="H8" t="n">
-        <v>390.85</v>
+        <v>383.7</v>
       </c>
       <c r="I8" t="n">
         <v>384.7121961703864</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.08</v>
+        <v>-3.87</v>
       </c>
       <c r="L8" t="n">
         <v>4.91</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.37</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H9" t="n">
-        <v>362.95</v>
+        <v>376.3</v>
       </c>
       <c r="I9" t="n">
         <v>375.1978979950728</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K9" t="n">
-        <v>5.41</v>
+        <v>1.93</v>
       </c>
       <c r="L9" t="n">
         <v>2.28</v>
@@ -954,7 +1061,7 @@
         <v>0.76</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="O9" t="n">
         <v>-1.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.16</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43600</v>
+        <v>43601</v>
       </c>
       <c r="H10" t="n">
-        <v>388.3</v>
+        <v>379.9</v>
       </c>
       <c r="I10" t="n">
         <v>384.1762965352072</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K10" t="n">
-        <v>3.19</v>
+        <v>0.96</v>
       </c>
       <c r="L10" t="n">
         <v>5.55</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.81</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H11" t="n">
-        <v>407.95</v>
+        <v>422.6</v>
       </c>
       <c r="I11" t="n">
         <v>408.9859531589255</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.38</v>
+        <v>-11.24</v>
       </c>
       <c r="L11" t="n">
-        <v>8.380000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="M11" t="n">
         <v>2.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H12" t="n">
-        <v>580.15</v>
+        <v>567.9</v>
       </c>
       <c r="I12" t="n">
         <v>573.5701833980411</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K12" t="n">
-        <v>37.28</v>
+        <v>34.38</v>
       </c>
       <c r="L12" t="n">
         <v>3.79</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>11.78</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43818</v>
+        <v>43819</v>
       </c>
       <c r="H13" t="n">
-        <v>605.25</v>
+        <v>612.7</v>
       </c>
       <c r="I13" t="n">
         <v>609.9474405748987</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.58</v>
+        <v>-7.89</v>
       </c>
       <c r="L13" t="n">
-        <v>7.28</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>0.8100000000000001</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.88</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H14" t="n">
-        <v>599.2</v>
+        <v>562.4</v>
       </c>
       <c r="I14" t="n">
         <v>595.7893787032991</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.2</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>3.03</v>
+        <v>12.21</v>
       </c>
       <c r="M14" t="n">
         <v>1.31</v>
       </c>
       <c r="N14" t="n">
-        <v>1.78</v>
+        <v>6.14</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.54</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H15" t="n">
-        <v>471.7</v>
+        <v>489.7</v>
       </c>
       <c r="I15" t="n">
         <v>486.0184401054507</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K15" t="n">
-        <v>16.13</v>
+        <v>12.93</v>
       </c>
       <c r="L15" t="n">
         <v>8.289999999999999</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>24.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44056</v>
+        <v>44057</v>
       </c>
       <c r="H16" t="n">
-        <v>599.75</v>
+        <v>587.75</v>
       </c>
       <c r="I16" t="n">
         <v>588.6391377507764</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K16" t="n">
-        <v>22.47</v>
+        <v>20.02</v>
       </c>
       <c r="L16" t="n">
         <v>7.87</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.76</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H17" t="n">
-        <v>592.85</v>
+        <v>609.65</v>
       </c>
       <c r="I17" t="n">
         <v>602.4106345346094</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.87</v>
+        <v>-3.73</v>
       </c>
       <c r="L17" t="n">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="M17" t="n">
         <v>1.54</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.95</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H18" t="n">
-        <v>682.85</v>
+        <v>671.8</v>
       </c>
       <c r="I18" t="n">
         <v>672.6024403631957</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K18" t="n">
-        <v>12.01</v>
+        <v>10.19</v>
       </c>
       <c r="L18" t="n">
         <v>3.16</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.67</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44251</v>
+        <v>44252</v>
       </c>
       <c r="H19" t="n">
-        <v>718.8</v>
+        <v>733.5</v>
       </c>
       <c r="I19" t="n">
         <v>729.7367204113712</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>-7</v>
+        <v>-9.18</v>
       </c>
       <c r="L19" t="n">
-        <v>8.130000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="M19" t="n">
         <v>1.64</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.57</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H20" t="n">
-        <v>683.55</v>
+        <v>676.5</v>
       </c>
       <c r="I20" t="n">
         <v>678.9538602541575</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.81</v>
+        <v>-7.77</v>
       </c>
       <c r="L20" t="n">
         <v>8.130000000000001</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.58</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H21" t="n">
-        <v>692.15</v>
+        <v>700.3</v>
       </c>
       <c r="I21" t="n">
         <v>697.5747074851548</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.31</v>
+        <v>-3.52</v>
       </c>
       <c r="L21" t="n">
         <v>6.28</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>6.11</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44375</v>
+        <v>44376</v>
       </c>
       <c r="H22" t="n">
-        <v>696.2</v>
+        <v>686.5</v>
       </c>
       <c r="I22" t="n">
         <v>688.8258997229516</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.59</v>
+        <v>-1.97</v>
       </c>
       <c r="L22" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9</v>
+        <v>2.29</v>
       </c>
       <c r="N22" t="n">
         <v>4.1</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.26</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44433</v>
+        <v>44434</v>
       </c>
       <c r="H23" t="n">
-        <v>687.55</v>
+        <v>698.85</v>
       </c>
       <c r="I23" t="n">
         <v>696.4396568271801</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.15</v>
+        <v>-1.8</v>
       </c>
       <c r="L23" t="n">
         <v>2.33</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.38</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44480</v>
+        <v>44481</v>
       </c>
       <c r="H24" t="n">
-        <v>717.3</v>
+        <v>703.4</v>
       </c>
       <c r="I24" t="n">
         <v>704.141597010179</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K24" t="n">
-        <v>2.64</v>
+        <v>0.65</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.81</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H25" t="n">
-        <v>550.35</v>
+        <v>571.8</v>
       </c>
       <c r="I25" t="n">
         <v>558.3154811190739</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K25" t="n">
-        <v>21.76</v>
+        <v>18.71</v>
       </c>
       <c r="L25" t="n">
         <v>2.92</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44728</v>
+        <v>44729</v>
       </c>
       <c r="H26" t="n">
-        <v>570.55</v>
+        <v>550.8</v>
       </c>
       <c r="I26" t="n">
         <v>558.6875454991798</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.22</v>
+        <v>-3.67</v>
       </c>
       <c r="L26" t="n">
         <v>8.109999999999999</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.38</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44785</v>
+        <v>44789</v>
       </c>
       <c r="H27" t="n">
-        <v>544.95</v>
+        <v>570.6</v>
       </c>
       <c r="I27" t="n">
         <v>562.0952189002187</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K27" t="n">
-        <v>1.06</v>
+        <v>-3.59</v>
       </c>
       <c r="L27" t="n">
         <v>5.52</v>
@@ -1980,7 +2303,7 @@
         <v>1.58</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="O27" t="n">
         <v>-3.46</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>8.76</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H28" t="n">
-        <v>566.75</v>
+        <v>546.75</v>
       </c>
       <c r="I28" t="n">
         <v>553.9326757711053</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.67</v>
+        <v>-4.18</v>
       </c>
       <c r="L28" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="M28" t="n">
         <v>2.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.82</v>
+        <v>3.53</v>
       </c>
       <c r="O28" t="n">
         <v>4.71</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.09</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44888</v>
+        <v>44889</v>
       </c>
       <c r="H29" t="n">
-        <v>547.65</v>
+        <v>572.55</v>
       </c>
       <c r="I29" t="n">
         <v>556.7299038754512</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.16</v>
+        <v>-4.72</v>
       </c>
       <c r="L29" t="n">
-        <v>4.04</v>
+        <v>4.9</v>
       </c>
       <c r="M29" t="n">
         <v>2.64</v>
       </c>
       <c r="N29" t="n">
-        <v>2.73</v>
+        <v>4.55</v>
       </c>
       <c r="O29" t="n">
         <v>-3.53</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>7.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H30" t="n">
-        <v>578.85</v>
+        <v>515.7</v>
       </c>
       <c r="I30" t="n">
         <v>574.8187852258374</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K30" t="n">
-        <v>1.1</v>
+        <v>-9.93</v>
       </c>
       <c r="L30" t="n">
-        <v>3.92</v>
+        <v>12.26</v>
       </c>
       <c r="M30" t="n">
         <v>0.76</v>
       </c>
       <c r="N30" t="n">
-        <v>2.43</v>
+        <v>10.91</v>
       </c>
       <c r="O30" t="n">
         <v>4.55</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>16.74</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H31" t="n">
-        <v>495.95</v>
+        <v>499.2</v>
       </c>
       <c r="I31" t="n">
         <v>499.1930100977516</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K31" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
         <v>13.37</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H32" t="n">
-        <v>632.75</v>
+        <v>625.15</v>
       </c>
       <c r="I32" t="n">
         <v>628.2102531444903</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K32" t="n">
-        <v>26.75</v>
+        <v>25.23</v>
       </c>
       <c r="L32" t="n">
         <v>0.84</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.98</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H33" t="n">
-        <v>657.45</v>
+        <v>668.65</v>
       </c>
       <c r="I33" t="n">
         <v>658.5945280702465</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.17</v>
+        <v>-6.96</v>
       </c>
       <c r="L33" t="n">
-        <v>5.7</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M33" t="n">
         <v>0.62</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>5.82</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="H34" t="n">
-        <v>633.55</v>
+        <v>625.5</v>
       </c>
       <c r="I34" t="n">
         <v>629.7087261604559</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.25</v>
+        <v>-6.45</v>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>6.64</v>
       </c>
       <c r="M34" t="n">
         <v>0.75</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.19</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45247</v>
+        <v>45250</v>
       </c>
       <c r="H35" t="n">
-        <v>651.8</v>
+        <v>652.4</v>
       </c>
       <c r="I35" t="n">
         <v>651.8033514499886</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="L35" t="n">
         <v>5.52</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>5.82</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H36" t="n">
-        <v>666.05</v>
+        <v>644.1</v>
       </c>
       <c r="I36" t="n">
         <v>651.8931202313468</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>2.09</v>
+        <v>-1.27</v>
       </c>
       <c r="L36" t="n">
-        <v>0.75</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
         <v>0.12</v>
       </c>
       <c r="N36" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0.09</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="H37" t="n">
-        <v>607.7</v>
+        <v>613.95</v>
       </c>
       <c r="I37" t="n">
         <v>613.9243771210261</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K37" t="n">
-        <v>5.65</v>
+        <v>4.68</v>
       </c>
       <c r="L37" t="n">
         <v>4.64</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.62</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45405</v>
+        <v>45406</v>
       </c>
       <c r="H38" t="n">
-        <v>601.15</v>
+        <v>594.2</v>
       </c>
       <c r="I38" t="n">
         <v>598.3768210608342</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.08</v>
+        <v>-3.22</v>
       </c>
       <c r="L38" t="n">
         <v>5.35</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H39" t="n">
-        <v>572.7</v>
+        <v>593.5</v>
       </c>
       <c r="I39" t="n">
         <v>581.5096871515827</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>3.62</v>
+        <v>0.12</v>
       </c>
       <c r="L39" t="n">
         <v>1.55</v>
@@ -2664,7 +3131,7 @@
         <v>3.47</v>
       </c>
       <c r="N39" t="n">
-        <v>3.27</v>
+        <v>3.63</v>
       </c>
       <c r="O39" t="n">
         <v>-1.16</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.98</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H40" t="n">
-        <v>735.8</v>
+        <v>702.9</v>
       </c>
       <c r="I40" t="n">
         <v>707.4771626880815</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K40" t="n">
-        <v>23.98</v>
+        <v>18.43</v>
       </c>
       <c r="L40" t="n">
         <v>4.8</v>
@@ -2721,7 +3200,7 @@
         <v>3.16</v>
       </c>
       <c r="N40" t="n">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="O40" t="n">
         <v>3.63</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H41" t="n">
-        <v>742.45</v>
+        <v>745.85</v>
       </c>
       <c r="I41" t="n">
         <v>743.7196825026954</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.63</v>
+        <v>-6.11</v>
       </c>
       <c r="L41" t="n">
-        <v>6.2</v>
+        <v>7.48</v>
       </c>
       <c r="M41" t="n">
         <v>1.29</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>6.54</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H42" t="n">
-        <v>700</v>
+        <v>685.05</v>
       </c>
       <c r="I42" t="n">
         <v>697.0358475110727</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.15</v>
+        <v>-8.15</v>
       </c>
       <c r="L42" t="n">
-        <v>8.1</v>
+        <v>8.41</v>
       </c>
       <c r="M42" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="N42" t="n">
         <v>2.37</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.99</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45672</v>
+        <v>45673</v>
       </c>
       <c r="H43" t="n">
-        <v>594.2</v>
+        <v>641.4</v>
       </c>
       <c r="I43" t="n">
         <v>632.3717486803524</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K43" t="n">
-        <v>13.26</v>
+        <v>6.37</v>
       </c>
       <c r="L43" t="n">
         <v>2.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.87</v>
+        <v>6.04</v>
       </c>
       <c r="N43" t="n">
-        <v>2.56</v>
+        <v>7.94</v>
       </c>
       <c r="O43" t="n">
         <v>-2.14</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.81</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H44" t="n">
-        <v>771.25</v>
+        <v>759</v>
       </c>
       <c r="I44" t="n">
         <v>766.5442671532901</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K44" t="n">
-        <v>20.24</v>
+        <v>18.33</v>
       </c>
       <c r="L44" t="n">
         <v>7.2</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.43</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="H45" t="n">
-        <v>776.6</v>
+        <v>788.75</v>
       </c>
       <c r="I45" t="n">
         <v>780.5853098008272</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.32</v>
+        <v>-3.92</v>
       </c>
       <c r="L45" t="n">
-        <v>3.25</v>
+        <v>4.18</v>
       </c>
       <c r="M45" t="n">
         <v>1.08</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.1</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="H46" t="n">
-        <v>776.45</v>
+        <v>754.25</v>
       </c>
       <c r="I46" t="n">
         <v>754.9681550314837</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.56</v>
+        <v>-4.37</v>
       </c>
       <c r="L46" t="n">
-        <v>2.8</v>
+        <v>4.91</v>
       </c>
       <c r="M46" t="n">
         <v>0.51</v>
       </c>
       <c r="N46" t="n">
-        <v>1.32</v>
+        <v>2.86</v>
       </c>
       <c r="O46" t="n">
         <v>1.56</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.38</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="H47" t="n">
-        <v>763.9</v>
+        <v>783.1</v>
       </c>
       <c r="I47" t="n">
         <v>775.9988406891445</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.28</v>
+        <v>-3.82</v>
       </c>
       <c r="L47" t="n">
         <v>6.46</v>
@@ -3120,7 +3683,7 @@
         <v>3.42</v>
       </c>
       <c r="N47" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="O47" t="n">
         <v>-2.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="H48" t="n">
-        <v>743.2</v>
+        <v>732.55</v>
       </c>
       <c r="I48" t="n">
         <v>741.8087273942517</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.1</v>
+        <v>-6.46</v>
       </c>
       <c r="L48" t="n">
-        <v>6.05</v>
+        <v>8.31</v>
       </c>
       <c r="M48" t="n">
         <v>0.87</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.82</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="H49" t="n">
-        <v>728.65</v>
+        <v>742.45</v>
       </c>
       <c r="I49" t="n">
         <v>738.5144171398473</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K49" t="n">
-        <v>0.53</v>
+        <v>-1.35</v>
       </c>
       <c r="L49" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
         <v>0.5600000000000001</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.39</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H50" t="n">
-        <v>707.3</v>
+        <v>684.6</v>
       </c>
       <c r="I50" t="n">
         <v>697.6588330620398</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.73</v>
+        <v>-7.79</v>
       </c>
       <c r="L50" t="n">
-        <v>5.31</v>
+        <v>8.16</v>
       </c>
       <c r="M50" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="N50" t="n">
-        <v>2.55</v>
+        <v>3.21</v>
       </c>
       <c r="O50" t="n">
         <v>1.89</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H51" t="n">
-        <v>619.1</v>
+        <v>640.45</v>
       </c>
       <c r="I51" t="n">
         <v>619.5274465070287</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>9.57</v>
+        <v>6.45</v>
       </c>
       <c r="L51" t="n">
         <v>3.29</v>
@@ -3348,7 +3959,7 @@
         <v>2.29</v>
       </c>
       <c r="N51" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="O51" t="n">
         <v>-3.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>10.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H52" t="n">
-        <v>586.55</v>
+        <v>579.9</v>
       </c>
       <c r="I52" t="n">
         <v>583.8765101820442</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.42</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>9.69</v>
+        <v>10.79</v>
       </c>
       <c r="M52" t="n">
         <v>1.99</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.21</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H53" t="n">
-        <v>581.8</v>
+        <v>591.3</v>
       </c>
       <c r="I53" t="n">
         <v>587.4386434994485</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.33</v>
+        <v>-1.97</v>
       </c>
       <c r="L53" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="M53" t="n">
         <v>1.24</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.67</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H54" t="n">
-        <v>572.45</v>
+        <v>555.7</v>
       </c>
       <c r="I54" t="n">
         <v>562.1919590418577</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.19</v>
+        <v>-6.02</v>
       </c>
       <c r="L54" t="n">
-        <v>5.3</v>
+        <v>6.45</v>
       </c>
       <c r="M54" t="n">
         <v>0.9</v>
       </c>
       <c r="N54" t="n">
-        <v>1.27</v>
+        <v>2.93</v>
       </c>
       <c r="O54" t="n">
         <v>1.63</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="H55" t="n">
-        <v>530.2</v>
+        <v>557</v>
       </c>
       <c r="I55" t="n">
         <v>555.2569841830758</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K55" t="n">
-        <v>4.59</v>
+        <v>-0.23</v>
       </c>
       <c r="L55" t="n">
         <v>5.81</v>
@@ -3576,7 +4235,7 @@
         <v>2.86</v>
       </c>
       <c r="N55" t="n">
-        <v>2.87</v>
+        <v>5.05</v>
       </c>
       <c r="O55" t="n">
         <v>-2.93</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.22</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="H56" t="n">
-        <v>523.75</v>
+        <v>519</v>
       </c>
       <c r="I56" t="n">
         <v>520.1856838043857</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.97</v>
+        <v>-6.82</v>
       </c>
       <c r="L56" t="n">
         <v>8.17</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>3</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7495,7 +8186,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.5</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="6">
@@ -7505,7 +8196,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -7515,7 +8206,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -7525,7 +8216,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -7535,7 +8226,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="10">
@@ -7545,7 +8236,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -7555,7 +8246,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -7565,7 +8256,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -7575,7 +8266,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.6</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="14">
@@ -7585,7 +8276,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.95</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="15">
@@ -7595,7 +8286,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.99</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="16">
@@ -7605,7 +8296,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.88</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="17">
@@ -7615,7 +8306,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37.28</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="18">
@@ -7625,7 +8316,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="19">
@@ -7635,7 +8326,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.16</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="20">
@@ -7645,7 +8336,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.3</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="21">
@@ -7655,7 +8346,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.37</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="22">
@@ -7665,7 +8356,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -7675,7 +8366,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -7685,7 +8376,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="25">
@@ -7705,7 +8396,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.62</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="27">
@@ -7725,7 +8416,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
